--- a/dados/SURVEY_VESSELS/SURVEY_VESSELS_20260727_noite.xlsx
+++ b/dados/SURVEY_VESSELS/SURVEY_VESSELS_20260727_noite.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cefetrjbr-my.sharepoint.com/personal/12396387790_cefet-rj_br/Documents/Empresas e entrevistas/projeto logistica offshore/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cefetrjbr-my.sharepoint.com/personal/12396387790_cefet-rj_br/Documents/Empresas e entrevistas/projeto logistica offshore/ofi/dados/SURVEY_VESSELS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="86" documentId="8_{DD1E2704-A9C5-456B-A053-C635EBA8AB6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46D17287-7802-4E0E-8BA5-93AEB30D050C}"/>
+  <xr:revisionPtr revIDLastSave="88" documentId="8_{DD1E2704-A9C5-456B-A053-C635EBA8AB6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2F3ED21-5696-45CA-BF5A-CA796733E14B}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="2" xr2:uid="{FAEFD476-B005-4995-A964-6D919B2AA8E5}"/>
+    <workbookView xWindow="1776" yWindow="1776" windowWidth="17280" windowHeight="8880" activeTab="3" xr2:uid="{FAEFD476-B005-4995-A964-6D919B2AA8E5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="72">
   <si>
     <t>cbo</t>
   </si>
@@ -2048,6 +2048,21 @@
       <c r="A7" t="s">
         <v>54</v>
       </c>
+      <c r="B7" s="4">
+        <v>46230.87222222222</v>
+      </c>
+      <c r="D7" s="1">
+        <v>-24.050816999999999</v>
+      </c>
+      <c r="E7" s="1">
+        <v>-42.173805000000002</v>
+      </c>
+      <c r="F7" s="4">
+        <v>46230.347916666666</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="I7" s="1"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
